--- a/plantillas/consulta/Reporte_Asistencia.xlsx
+++ b/plantillas/consulta/Reporte_Asistencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5038A6-589D-423C-B13F-7F11ABA8EB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9B85F0-AD23-4406-A25E-5C953D4FA413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -82,14 +82,15 @@
     <t>Hora de Modificación</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -139,6 +140,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -211,12 +218,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -226,10 +234,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,34 +567,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
@@ -603,49 +610,49 @@
       <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-    </row>
-    <row r="7" spans="1:11" s="15" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -654,16 +661,16 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="5"/>
       <c r="E9" s="4"/>
       <c r="H9" s="2"/>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -674,37 +681,37 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>5</v>
       </c>
     </row>

--- a/plantillas/consulta/Reporte_Asistencia.xlsx
+++ b/plantillas/consulta/Reporte_Asistencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9B85F0-AD23-4406-A25E-5C953D4FA413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623F8BB8-4927-481A-A54F-24C6F10D6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
@@ -225,6 +225,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -233,9 +236,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -567,34 +567,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
@@ -610,34 +610,34 @@
       <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
@@ -661,7 +661,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -670,7 +670,7 @@
       <c r="B9" s="5"/>
       <c r="E9" s="4"/>
       <c r="H9" s="2"/>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="12" t="s">
         <v>8</v>
       </c>
     </row>
